--- a/src/rodos_corpus/data/corpus/rendered/finance/REESTR-PLAT-20260922.xlsx
+++ b/src/rodos_corpus/data/corpus/rendered/finance/REESTR-PLAT-20260922.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3502000</v>
+        <v>1155000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -521,11 +521,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1155000</v>
+        <v>885000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Финансовый директор</t>
+          <t>Главный бухгалтер</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>885000</v>
+        <v>767000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -567,25 +567,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KMP-2025/02</t>
+          <t>БМК-2025/11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ТОО «KazMashParts»</t>
+          <t>ООО «Балтмашкомплект»</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>000000123456</t>
+          <t>007806334455</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>767000</v>
+        <v>2082000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Главный бухгалтер</t>
+          <t>Финансовый директор</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2082000</v>
+        <v>3105000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -620,28 +620,28 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>оплачено</t>
+          <t>к оплате</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ЛЛ-2025/05</t>
+          <t>СГМ-2026/05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ООО «Логистик-Лайн»</t>
+          <t>ООО «Сибгидромаш»</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>006316112233</t>
+          <t>005503221144</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3105000</v>
+        <v>2998000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>к оплате</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2998000</v>
+        <v>3983000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -680,28 +680,28 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>оплачено</t>
+          <t>к оплате</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ТНЭ-2024/19</t>
+          <t>ПНН-2025/08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ООО «Технадзор-Эксперт»</t>
+          <t>ООО «Привод-НН»</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005903334455</t>
+          <t>005261334455</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3983000</v>
+        <v>1863000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -710,28 +710,28 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>к оплате</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>УМС-2025/03</t>
+          <t>АЦ-2024/45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>АО «Уралметснаб»</t>
+          <t>ООО «Абразив-Центр»</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>006612345678</t>
+          <t>006452003311</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1863000</v>
+        <v>2383000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>20340000</v>
+        <v>19221000</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
